--- a/SMARTX/Porewater/1-Sulfide/2026/Datasheets/2026July_SMARTX_H2S_Datasheets.xlsx
+++ b/SMARTX/Porewater/1-Sulfide/2026/Datasheets/2026July_SMARTX_H2S_Datasheets.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\GlobalChangeEco\Porewater_R scripts &amp; Data\Data\Sulfide Microplate\SMARTX\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/giessnerm_si_edu/Documents/Documents/GitHub/GCREW/SMARTX/Porewater/1-Sulfide/2026/Datasheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEF06FC-72E9-4200-8D69-5C83A8E3170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{2EEF06FC-72E9-4200-8D69-5C83A8E3170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B292E0D-B1C2-4E69-A874-3D071F0560E9}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="1320" windowWidth="17895" windowHeight="12600" firstSheet="1" activeTab="1" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
+    <workbookView xWindow="345" yWindow="1455" windowWidth="16590" windowHeight="11295" firstSheet="5" activeTab="10" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
   </bookViews>
   <sheets>
     <sheet name="STD 1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="205">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="206">
   <si>
     <t>A</t>
   </si>
@@ -115,9 +115,6 @@
     <t>ChkStd 4</t>
   </si>
   <si>
-    <t>Spike</t>
-  </si>
-  <si>
     <t>610-10</t>
   </si>
   <si>
@@ -662,6 +659,12 @@
   </si>
   <si>
     <t>Melanie</t>
+  </si>
+  <si>
+    <t>461-80 Spike</t>
+  </si>
+  <si>
+    <t>463-80 Spike</t>
   </si>
 </sst>
 </file>
@@ -1603,31 +1606,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -1644,13 +1647,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -1662,13 +1665,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -1686,31 +1689,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -1728,13 +1731,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -1746,13 +1749,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -1770,31 +1773,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -1815,13 +1818,13 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -1851,22 +1854,22 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -1875,31 +1878,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -2352,28 +2355,32 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
+        <v>202</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
@@ -2389,13 +2396,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -2425,22 +2432,22 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
@@ -2461,13 +2468,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -2479,13 +2486,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>22</v>
+        <v>204</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -2503,31 +2510,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>22</v>
+        <v>205</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -2545,22 +2552,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -2587,22 +2594,22 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
@@ -2614,31 +2621,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -3029,7 +3036,7 @@
         <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -3037,7 +3044,7 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3111,31 +3118,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -3152,13 +3159,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -3170,13 +3177,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -3194,31 +3201,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -3236,13 +3243,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -3254,13 +3261,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -3278,31 +3285,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -3320,22 +3327,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -3362,31 +3369,31 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -3395,31 +3402,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -3872,31 +3879,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -3913,13 +3920,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -3931,13 +3938,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -3955,31 +3962,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -3997,13 +4004,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -4015,13 +4022,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -4039,31 +4046,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -4081,22 +4088,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -4123,31 +4130,31 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -4156,31 +4163,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -4633,31 +4640,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -4674,13 +4681,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -4692,13 +4699,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -4716,31 +4723,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -4758,13 +4765,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -4776,13 +4783,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -4800,31 +4807,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -4842,22 +4849,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -4884,31 +4891,31 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -4917,31 +4924,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -5394,31 +5401,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -5435,13 +5442,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -5453,13 +5460,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -5477,31 +5484,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -5519,13 +5526,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -5537,13 +5544,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -5561,31 +5568,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -5603,22 +5610,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -5645,31 +5652,31 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -5678,31 +5685,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -6155,31 +6162,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -6196,13 +6203,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -6214,13 +6221,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -6238,31 +6245,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -6280,13 +6287,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -6298,13 +6305,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -6322,31 +6329,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -6364,22 +6371,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -6406,31 +6413,31 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -6439,31 +6446,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -7376,31 +7383,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -7417,13 +7424,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -7435,13 +7442,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -7459,31 +7466,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -7501,13 +7508,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -7519,13 +7526,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -7543,31 +7550,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -7585,22 +7592,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -7627,31 +7634,31 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -7660,31 +7667,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>
@@ -8137,31 +8144,31 @@
         <v>1</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
@@ -8178,13 +8185,13 @@
         <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>19</v>
@@ -8196,13 +8203,13 @@
         <v>19</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N3" s="3"/>
     </row>
@@ -8220,31 +8227,31 @@
         <v>5</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N4" s="3"/>
     </row>
@@ -8262,13 +8269,13 @@
         <v>7</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>20</v>
@@ -8280,13 +8287,13 @@
         <v>20</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N5" s="3"/>
     </row>
@@ -8304,31 +8311,31 @@
         <v>9</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N6" s="3"/>
     </row>
@@ -8346,22 +8353,22 @@
         <v>11</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>19</v>
@@ -8388,31 +8395,31 @@
         <v>13</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N8" s="3"/>
     </row>
@@ -8421,31 +8428,31 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>21</v>

--- a/SMARTX/Porewater/1-Sulfide/2026/Datasheets/2026July_SMARTX_H2S_Datasheets.xlsx
+++ b/SMARTX/Porewater/1-Sulfide/2026/Datasheets/2026July_SMARTX_H2S_Datasheets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sinet-my.sharepoint.com/personal/giessnerm_si_edu/Documents/Documents/GitHub/GCREW/SMARTX/Porewater/1-Sulfide/2026/Datasheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{2EEF06FC-72E9-4200-8D69-5C83A8E3170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B292E0D-B1C2-4E69-A874-3D071F0560E9}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{2EEF06FC-72E9-4200-8D69-5C83A8E3170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E719769-201F-445D-9122-38E7F7C81F27}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="1455" windowWidth="16590" windowHeight="11295" firstSheet="5" activeTab="10" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
+    <workbookView xWindow="375" yWindow="135" windowWidth="17805" windowHeight="13380" firstSheet="8" activeTab="14" xr2:uid="{23FB6DB2-3641-4E78-A68E-113D11F8B05A}"/>
   </bookViews>
   <sheets>
     <sheet name="STD 1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,10 @@
     <sheet name="Plate 7" sheetId="9" r:id="rId9"/>
     <sheet name="Plate 8" sheetId="10" r:id="rId10"/>
     <sheet name="Plate 9" sheetId="11" r:id="rId11"/>
-    <sheet name="QAQC" sheetId="2" r:id="rId12"/>
+    <sheet name="STD 5" sheetId="13" r:id="rId12"/>
+    <sheet name="Rerun1" sheetId="14" r:id="rId13"/>
+    <sheet name="Rerun2" sheetId="15" r:id="rId14"/>
+    <sheet name="QAQC" sheetId="2" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1083" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="220">
   <si>
     <t>A</t>
   </si>
@@ -665,6 +668,48 @@
   </si>
   <si>
     <t>463-80 Spike</t>
+  </si>
+  <si>
+    <t>Sp10-40</t>
+  </si>
+  <si>
+    <t>Ch6-80</t>
+  </si>
+  <si>
+    <t>Ch12-5</t>
+  </si>
+  <si>
+    <t>Ch7-5</t>
+  </si>
+  <si>
+    <t>Ch5-40</t>
+  </si>
+  <si>
+    <t>Ch6-80 Dup</t>
+  </si>
+  <si>
+    <t>Sp13-20</t>
+  </si>
+  <si>
+    <t>Sc8-80</t>
+  </si>
+  <si>
+    <t>Ch7-80</t>
+  </si>
+  <si>
+    <t>Ch10-70</t>
+  </si>
+  <si>
+    <t>Ch12-40</t>
+  </si>
+  <si>
+    <t>Sp4-20</t>
+  </si>
+  <si>
+    <t>Ch12-80</t>
+  </si>
+  <si>
+    <t>P3-20</t>
   </si>
 </sst>
 </file>
@@ -791,6 +836,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3023,6 +3072,1554 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B86F113D-9EF8-4395-8609-8F36784CAF3F}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+      <c r="K12" s="5"/>
+      <c r="L12" s="5"/>
+      <c r="M12" s="5"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="5"/>
+      <c r="L13" s="5"/>
+      <c r="M13" s="5"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+      <c r="K14" s="5"/>
+      <c r="L14" s="5"/>
+      <c r="M14" s="5"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="5"/>
+      <c r="M15" s="5"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+      <c r="K16" s="5"/>
+      <c r="L16" s="5"/>
+      <c r="M16" s="5"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
+      <c r="L18" s="5"/>
+      <c r="M18" s="5"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C4585F-42F1-4B0A-AA90-833F23FFA9E9}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="J8" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J9" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="M9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>50</v>
+      </c>
+      <c r="F12" s="4">
+        <v>50</v>
+      </c>
+      <c r="G12" s="4">
+        <v>50</v>
+      </c>
+      <c r="H12" s="4">
+        <v>250</v>
+      </c>
+      <c r="I12" s="4">
+        <v>250</v>
+      </c>
+      <c r="J12" s="4">
+        <v>250</v>
+      </c>
+      <c r="K12" s="4">
+        <v>1</v>
+      </c>
+      <c r="L12" s="4">
+        <v>1</v>
+      </c>
+      <c r="M12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>50</v>
+      </c>
+      <c r="F13" s="4">
+        <v>50</v>
+      </c>
+      <c r="G13" s="4">
+        <v>50</v>
+      </c>
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4">
+        <v>1</v>
+      </c>
+      <c r="C14" s="4">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>50</v>
+      </c>
+      <c r="F14" s="4">
+        <v>50</v>
+      </c>
+      <c r="G14" s="4">
+        <v>50</v>
+      </c>
+      <c r="H14" s="4">
+        <v>250</v>
+      </c>
+      <c r="I14" s="4">
+        <v>250</v>
+      </c>
+      <c r="J14" s="4">
+        <v>250</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4">
+        <v>25</v>
+      </c>
+      <c r="G15" s="4">
+        <v>25</v>
+      </c>
+      <c r="H15" s="4">
+        <v>1</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+      <c r="J15" s="4">
+        <v>1</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4">
+        <v>1</v>
+      </c>
+      <c r="C16" s="4">
+        <v>1</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>250</v>
+      </c>
+      <c r="F16" s="4">
+        <v>250</v>
+      </c>
+      <c r="G16" s="4">
+        <v>250</v>
+      </c>
+      <c r="H16" s="4">
+        <v>100</v>
+      </c>
+      <c r="I16" s="4">
+        <v>100</v>
+      </c>
+      <c r="J16" s="4">
+        <v>100</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4">
+        <v>1</v>
+      </c>
+      <c r="C17" s="4">
+        <v>1</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>250</v>
+      </c>
+      <c r="F17" s="4">
+        <v>250</v>
+      </c>
+      <c r="G17" s="4">
+        <v>250</v>
+      </c>
+      <c r="H17" s="4">
+        <v>100</v>
+      </c>
+      <c r="I17" s="4">
+        <v>100</v>
+      </c>
+      <c r="J17" s="4">
+        <v>100</v>
+      </c>
+      <c r="K17" s="4">
+        <v>1</v>
+      </c>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4">
+        <v>1</v>
+      </c>
+      <c r="C18" s="4">
+        <v>1</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>250</v>
+      </c>
+      <c r="F18" s="4">
+        <v>250</v>
+      </c>
+      <c r="G18" s="4">
+        <v>250</v>
+      </c>
+      <c r="H18" s="4">
+        <v>250</v>
+      </c>
+      <c r="I18" s="4">
+        <v>250</v>
+      </c>
+      <c r="J18" s="4">
+        <v>250</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4">
+        <v>50</v>
+      </c>
+      <c r="C19" s="4">
+        <v>50</v>
+      </c>
+      <c r="D19" s="4">
+        <v>50</v>
+      </c>
+      <c r="E19" s="4">
+        <v>250</v>
+      </c>
+      <c r="F19" s="4">
+        <v>250</v>
+      </c>
+      <c r="G19" s="4">
+        <v>250</v>
+      </c>
+      <c r="H19" s="4">
+        <v>1</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+      <c r="J19" s="4">
+        <v>1</v>
+      </c>
+      <c r="K19" s="4">
+        <v>1</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E043D1DD-823D-4BCA-908F-4FDD57484649}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="5"/>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+      <c r="K8" s="5"/>
+      <c r="L8" s="5"/>
+      <c r="M8" s="5"/>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="2">
+        <v>1</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5</v>
+      </c>
+      <c r="G11" s="2">
+        <v>6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8</v>
+      </c>
+      <c r="J11" s="2">
+        <v>9</v>
+      </c>
+      <c r="K11" s="2">
+        <v>10</v>
+      </c>
+      <c r="L11" s="2">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4">
+        <v>25</v>
+      </c>
+      <c r="L14" s="4">
+        <v>25</v>
+      </c>
+      <c r="M14" s="4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74720A33-EA02-4F3B-99BC-21807D7702E9}">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
